--- a/template.xlsx
+++ b/template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,6 +856,264 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>az-server</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>azure</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>southeastasia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Standard_D2s_v5</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Linux</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>730</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Azure Web Server</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>az-nat</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>azure</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>southeastasia</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nat_gateway</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>100</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>730</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Azure NAT Gateway and 100GB data processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>az-vpn</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>azure</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>southeastasia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>vpn_gateway</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>730</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Azure VPN Gateway Connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>az-public-ip</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>azure</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>southeastasia</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>public_ip</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>730</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2 Azure Public Static IPs</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>az-asr</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>azure</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>southeastasia</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>site_recovery</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" t="n">
+        <v>55</v>
+      </c>
+      <c r="J15" t="n">
+        <v>730</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Azure Site Recovery to cloud (55 protected servers, 50GB storage each)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>az-custom</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>azure</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>southeastasia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Linux</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>730</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Cheapest custom Azure Linux VM matching &gt;= 2 vCPU and 4GB memory</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/template.xlsx
+++ b/template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1114,6 +1114,92 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>drs-drill1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>drs-drill</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ap-southeast-3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Linux</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>50</v>
+      </c>
+      <c r="I17" t="n">
+        <v>55</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>DR Drill test: 55 servers for 20 hours per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>app-alb</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>alb</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ap-southeast-3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>730</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Application Load Balancer with 1000GB data processed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
